--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -1341,7 +1341,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-01</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -648,10 +648,10 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>Observation.category:endoscopy</t>
-  </si>
-  <si>
-    <t>endoscopy</t>
+    <t>Observation.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
   </si>
   <si>
     <t>内視鏡検査の第1カテゴリはJP_SimpleObservationCategory_VSからprocedureを指定する。</t>
@@ -660,7 +660,7 @@
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
-    <t>Observation.category:endoscopy.id</t>
+    <t>Observation.category:first.id</t>
   </si>
   <si>
     <t>Observation.category.id</t>
@@ -682,7 +682,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Observation.category:endoscopy.extension</t>
+    <t>Observation.category:first.extension</t>
   </si>
   <si>
     <t>Observation.category.extension</t>
@@ -701,7 +701,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Observation.category:endoscopy.coding</t>
+    <t>Observation.category:first.coding</t>
   </si>
   <si>
     <t>Observation.category.coding</t>
@@ -732,19 +732,19 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Observation.category:endoscopy.coding.id</t>
+    <t>Observation.category:first.coding.id</t>
   </si>
   <si>
     <t>Observation.category.coding.id</t>
   </si>
   <si>
-    <t>Observation.category:endoscopy.coding.extension</t>
+    <t>Observation.category:first.coding.extension</t>
   </si>
   <si>
     <t>Observation.category.coding.extension</t>
   </si>
   <si>
-    <t>Observation.category:endoscopy.coding.system</t>
+    <t>Observation.category:first.coding.system</t>
   </si>
   <si>
     <t>Observation.category.coding.system</t>
@@ -774,7 +774,7 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>Observation.category:endoscopy.coding.version</t>
+    <t>Observation.category:first.coding.version</t>
   </si>
   <si>
     <t>Observation.category.coding.version</t>
@@ -798,7 +798,7 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>Observation.category:endoscopy.coding.code</t>
+    <t>Observation.category:first.coding.code</t>
   </si>
   <si>
     <t>Observation.category.coding.code</t>
@@ -825,7 +825,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>Observation.category:endoscopy.coding.display</t>
+    <t>Observation.category:first.coding.display</t>
   </si>
   <si>
     <t>Observation.category.coding.display</t>
@@ -849,7 +849,7 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>Observation.category:endoscopy.coding.userSelected</t>
+    <t>Observation.category:first.coding.userSelected</t>
   </si>
   <si>
     <t>Observation.category.coding.userSelected</t>
@@ -880,7 +880,7 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
-    <t>Observation.category:endoscopy.text</t>
+    <t>Observation.category:first.text</t>
   </si>
   <si>
     <t>Observation.category.text</t>
@@ -907,10 +907,10 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
-    <t>Observation.category:endoscopy_sub</t>
-  </si>
-  <si>
-    <t>endoscopy_sub</t>
+    <t>Observation.category:second</t>
+  </si>
+  <si>
+    <t>second</t>
   </si>
   <si>
     <t>第2カテゴリはLOINCのPartコードLP7796-8（内視鏡）固定とする。</t>
@@ -919,43 +919,43 @@
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationCategory_Endoscopy_VS</t>
   </si>
   <si>
-    <t>Observation.category:endoscopy_sub.id</t>
-  </si>
-  <si>
-    <t>Observation.category:endoscopy_sub.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:endoscopy_sub.coding</t>
-  </si>
-  <si>
-    <t>Observation.category:endoscopy_sub.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category:endoscopy_sub.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:endoscopy_sub.coding.system</t>
+    <t>Observation.category:second.id</t>
+  </si>
+  <si>
+    <t>Observation.category:second.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.system</t>
   </si>
   <si>
     <t>http://loinc.org</t>
   </si>
   <si>
-    <t>Observation.category:endoscopy_sub.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.category:endoscopy_sub.coding.code</t>
+    <t>Observation.category:second.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.code</t>
   </si>
   <si>
     <t>LP7796-8</t>
   </si>
   <si>
-    <t>Observation.category:endoscopy_sub.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.category:endoscopy_sub.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.category:endoscopy_sub.text</t>
+    <t>Observation.category:second.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.category:second.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.category:second.text</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -2015,9 +2015,9 @@
   <dimension ref="A1:AP75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="54.85546875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="47.2890625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.15234375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -285,7 +285,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -332,16 +332,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -467,7 +467,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -1404,7 +1404,7 @@
     <t>どの値が「正常」と見なされるかを知ることは、特定の結果の意義を評価するのに役立つ。さまざまなコンテキストに対応するため複数の参照範囲を提供できる必要がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="541">
   <si>
     <t>Property</t>
   </si>
@@ -632,7 +632,10 @@
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -657,7 +660,13 @@
     <t>内視鏡検査の第1カテゴリはJP_SimpleObservationCategory_VSからprocedureを指定する。</t>
   </si>
   <si>
-    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
+    <t>行われている一般的なタイプの観測を分類するコード。 / A code that classifies the general type of observation being made.</t>
+  </si>
+  <si>
+    <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -913,10 +922,13 @@
     <t>second</t>
   </si>
   <si>
-    <t>第2カテゴリはLOINCのPartコードLP7796-8（内視鏡）固定とする。</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationCategory_Endoscopy_VS</t>
+    <t>第2カテゴリはLOINCのPartコードLP7796-8（内視鏡）固定とする。ValueSetは指定しない。</t>
+  </si>
+  <si>
+    <t>第2カテゴリはLOINCのPartコードLP7796-8（内視鏡）固定とする。ValueSetのバインディングを指定していないことに注意すること。</t>
+  </si>
+  <si>
+    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
     <t>Observation.category:second.id</t>
@@ -2040,7 +2052,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.69140625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.41015625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -3817,22 +3829,24 @@
       <c r="X15" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y15" s="2"/>
+      <c r="Y15" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>190</v>
@@ -3859,10 +3873,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3870,13 +3884,13 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>190</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>83</v>
@@ -3886,7 +3900,7 @@
         <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>83</v>
@@ -3901,13 +3915,13 @@
         <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>196</v>
@@ -3939,7 +3953,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3981,10 +3995,10 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -3992,10 +4006,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4018,13 +4032,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4075,7 +4089,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4099,7 +4113,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4110,10 +4124,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4142,7 +4156,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4183,19 +4197,19 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4219,7 +4233,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4230,10 +4244,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4256,19 +4270,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4317,7 +4331,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4338,10 +4352,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4352,10 +4366,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4378,13 +4392,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4435,7 +4449,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4459,7 +4473,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4470,10 +4484,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4502,7 +4516,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4543,19 +4557,19 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4579,7 +4593,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4590,10 +4604,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4619,23 +4633,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4677,7 +4691,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4698,10 +4712,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4712,10 +4726,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4738,16 +4752,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4797,7 +4811,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4818,10 +4832,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4832,10 +4846,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4861,21 +4875,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4917,7 +4931,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4938,10 +4952,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4952,10 +4966,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4978,17 +4992,17 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5037,7 +5051,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5058,10 +5072,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5072,10 +5086,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5098,19 +5112,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5159,7 +5173,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5180,10 +5194,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5194,10 +5208,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5220,19 +5234,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5281,7 +5295,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5302,10 +5316,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5316,13 +5330,13 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>190</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>83</v>
@@ -5347,13 +5361,13 @@
         <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>194</v>
+        <v>293</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>205</v>
+        <v>294</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>196</v>
@@ -5381,11 +5395,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>290</v>
+        <v>198</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5427,10 +5443,10 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5438,10 +5454,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5464,13 +5480,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5521,7 +5537,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5545,7 +5561,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5556,10 +5572,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5588,7 +5604,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5629,19 +5645,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5665,7 +5681,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5676,10 +5692,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5702,19 +5718,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5763,7 +5779,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5784,10 +5800,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5798,10 +5814,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5824,13 +5840,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5881,7 +5897,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5905,7 +5921,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5916,10 +5932,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5948,7 +5964,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -5989,19 +6005,19 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6025,7 +6041,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6036,10 +6052,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6065,23 +6081,23 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6123,7 +6139,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6144,10 +6160,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6158,10 +6174,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6184,16 +6200,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6243,7 +6259,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6264,10 +6280,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6278,10 +6294,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6307,21 +6323,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6363,7 +6379,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6384,10 +6400,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6398,10 +6414,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6424,17 +6440,17 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6483,7 +6499,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6504,10 +6520,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6518,10 +6534,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6544,19 +6560,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6605,7 +6621,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6626,10 +6642,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6640,10 +6656,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6666,19 +6682,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6727,7 +6743,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6748,10 +6764,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6762,14 +6778,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6791,16 +6807,16 @@
         <v>192</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6829,7 +6845,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6847,7 +6863,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>94</v>
@@ -6862,30 +6878,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6908,19 +6924,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6969,7 +6985,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6984,19 +7000,19 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7004,10 +7020,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7030,16 +7046,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7089,7 +7105,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7110,13 +7126,13 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7124,14 +7140,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7150,19 +7166,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7211,7 +7227,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7226,19 +7242,19 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7246,14 +7262,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7272,19 +7288,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7333,7 +7349,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7348,19 +7364,19 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7368,10 +7384,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7394,16 +7410,16 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7453,7 +7469,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7474,13 +7490,13 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7488,10 +7504,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7514,19 +7530,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7575,7 +7591,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7590,19 +7606,19 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7610,10 +7626,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7636,19 +7652,19 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7673,11 +7689,11 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7695,7 +7711,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7704,7 +7720,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7713,27 +7729,27 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7759,16 +7775,16 @@
         <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7793,31 +7809,31 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF48" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="Z48" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7826,7 +7842,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7841,7 +7857,7 @@
         <v>137</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7852,14 +7868,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7881,16 +7897,16 @@
         <v>192</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7915,13 +7931,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7939,7 +7955,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7957,27 +7973,27 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8000,19 +8016,19 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8061,7 +8077,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8082,10 +8098,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8096,10 +8112,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8125,13 +8141,13 @@
         <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8157,31 +8173,31 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="Z51" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8199,27 +8215,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8245,16 +8261,16 @@
         <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8279,31 +8295,31 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8324,10 +8340,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8338,10 +8354,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8364,16 +8380,16 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8423,7 +8439,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8441,27 +8457,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8484,16 +8500,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8543,7 +8559,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8561,27 +8577,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8604,19 +8620,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8665,7 +8681,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8677,7 +8693,7 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8686,10 +8702,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8700,10 +8716,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8726,13 +8742,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8783,7 +8799,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8807,7 +8823,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8818,10 +8834,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8850,7 +8866,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -8903,7 +8919,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8927,7 +8943,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -8938,14 +8954,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8967,10 +8983,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -9025,7 +9041,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9060,10 +9076,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9086,13 +9102,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9143,7 +9159,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9152,7 +9168,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9164,10 +9180,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9178,10 +9194,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9204,13 +9220,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9261,7 +9277,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9270,7 +9286,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9282,10 +9298,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9296,10 +9312,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9325,16 +9341,16 @@
         <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9362,28 +9378,28 @@
         <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9401,13 +9417,13 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9418,10 +9434,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9447,16 +9463,16 @@
         <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9481,13 +9497,13 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9505,7 +9521,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9523,13 +9539,13 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9540,10 +9556,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9566,17 +9582,17 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9625,7 +9641,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9649,7 +9665,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9660,10 +9676,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9686,13 +9702,13 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9743,7 +9759,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9764,10 +9780,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9778,10 +9794,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9804,16 +9820,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9863,7 +9879,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9884,10 +9900,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9898,10 +9914,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9924,16 +9940,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9983,7 +9999,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10004,10 +10020,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10018,10 +10034,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10044,19 +10060,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10105,7 +10121,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10126,10 +10142,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10140,10 +10156,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10166,13 +10182,13 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10223,7 +10239,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10247,7 +10263,7 @@
         <v>83</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10258,10 +10274,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10290,7 +10306,7 @@
         <v>141</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>143</v>
@@ -10343,7 +10359,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10367,7 +10383,7 @@
         <v>83</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10378,14 +10394,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10407,10 +10423,10 @@
         <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>143</v>
@@ -10465,7 +10481,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10500,10 +10516,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10529,16 +10545,16 @@
         <v>192</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10563,31 +10579,31 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>94</v>
@@ -10605,16 +10621,16 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
@@ -10622,10 +10638,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10648,19 +10664,19 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10709,7 +10725,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10727,27 +10743,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10773,16 +10789,16 @@
         <v>192</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10807,13 +10823,13 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -10831,7 +10847,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10840,7 +10856,7 @@
         <v>94</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>106</v>
@@ -10855,7 +10871,7 @@
         <v>137</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -10866,14 +10882,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10895,16 +10911,16 @@
         <v>192</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10929,13 +10945,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -10953,7 +10969,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10971,27 +10987,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11017,16 +11033,16 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11075,7 +11091,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11096,10 +11112,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2914" uniqueCount="540">
   <si>
     <t>Property</t>
   </si>
@@ -1308,10 +1308,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -8175,11 +8172,9 @@
       <c r="X51" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="Y51" t="s" s="2">
+      <c r="Y51" s="2"/>
+      <c r="Z51" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8215,27 +8210,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>420</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8261,16 +8256,16 @@
         <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8298,11 +8293,11 @@
         <v>378</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>426</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8319,7 +8314,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8340,10 +8335,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8354,10 +8349,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8380,16 +8375,16 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8439,7 +8434,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8457,27 +8452,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>436</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8500,16 +8495,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8559,7 +8554,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8577,27 +8572,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP54" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>444</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8620,19 +8615,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8681,7 +8676,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8693,19 +8688,19 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AK55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8716,10 +8711,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8834,10 +8829,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8954,14 +8949,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8983,10 +8978,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -9041,7 +9036,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9076,10 +9071,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9102,13 +9097,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9159,7 +9154,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9168,7 +9163,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9180,10 +9175,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9194,10 +9189,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9220,13 +9215,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9277,7 +9272,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9286,7 +9281,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9298,10 +9293,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9312,10 +9307,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9341,16 +9336,16 @@
         <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9378,11 +9373,11 @@
         <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>476</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
       </c>
@@ -9399,7 +9394,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9417,10 +9412,10 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>403</v>
@@ -9434,10 +9429,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9463,16 +9458,16 @@
         <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9500,11 +9495,11 @@
         <v>378</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>485</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9521,7 +9516,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9539,10 +9534,10 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>403</v>
@@ -9556,10 +9551,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9582,17 +9577,17 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="L63" t="s" s="2">
-        <v>488</v>
-      </c>
       <c r="M63" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9641,7 +9636,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9665,7 +9660,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9676,10 +9671,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9705,10 +9700,10 @@
         <v>211</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9759,7 +9754,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9780,10 +9775,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9794,10 +9789,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9820,16 +9815,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9879,7 +9874,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9900,10 +9895,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9914,10 +9909,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9940,16 +9935,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9999,7 +9994,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10020,10 +10015,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10034,10 +10029,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10060,19 +10055,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10121,7 +10116,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10142,10 +10137,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10156,10 +10151,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10274,10 +10269,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10394,14 +10389,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10423,10 +10418,10 @@
         <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>143</v>
@@ -10481,7 +10476,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10516,10 +10511,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10545,13 +10540,13 @@
         <v>192</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>517</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="O71" t="s" s="2">
         <v>313</v>
@@ -10582,11 +10577,11 @@
         <v>378</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>520</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10603,7 +10598,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>94</v>
@@ -10621,7 +10616,7 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>317</v>
@@ -10638,10 +10633,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10664,16 +10659,16 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>377</v>
@@ -10725,7 +10720,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10743,7 +10738,7 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>382</v>
@@ -10760,10 +10755,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10789,13 +10784,13 @@
         <v>192</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>388</v>
@@ -10847,7 +10842,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10882,10 +10877,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10911,16 +10906,16 @@
         <v>192</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10969,7 +10964,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11004,10 +10999,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11033,16 +11028,16 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11091,7 +11086,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11112,10 +11107,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2914" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2914" uniqueCount="539">
   <si>
     <t>Property</t>
   </si>
@@ -922,10 +922,7 @@
     <t>second</t>
   </si>
   <si>
-    <t>第2カテゴリはLOINCのPartコードLP7796-8（内視鏡）固定とする。ValueSetは指定しない。</t>
-  </si>
-  <si>
-    <t>第2カテゴリはLOINCのPartコードLP7796-8（内視鏡）固定とする。ValueSetのバインディングを指定していないことに注意すること。</t>
+    <t>第2カテゴリはLOINCのPartコードLP7796-8（内視鏡）固定とする。ValueSetは指定しない</t>
   </si>
   <si>
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
@@ -5361,10 +5358,10 @@
         <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>196</v>
@@ -5451,7 +5448,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>210</v>
@@ -5569,7 +5566,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>217</v>
@@ -5689,7 +5686,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>223</v>
@@ -5811,7 +5808,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>233</v>
@@ -5929,7 +5926,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>235</v>
@@ -6049,7 +6046,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>237</v>
@@ -6094,7 +6091,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6171,7 +6168,7 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>247</v>
@@ -6291,7 +6288,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>255</v>
@@ -6334,7 +6331,7 @@
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6411,7 +6408,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>264</v>
@@ -6531,7 +6528,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>272</v>
@@ -6653,7 +6650,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>282</v>
@@ -6775,14 +6772,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6804,16 +6801,16 @@
         <v>192</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6842,7 +6839,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6860,7 +6857,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>94</v>
@@ -6875,30 +6872,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>320</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6921,19 +6918,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6982,7 +6979,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6997,19 +6994,19 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AL41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7017,10 +7014,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7043,16 +7040,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7102,7 +7099,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7123,13 +7120,13 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7137,14 +7134,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7163,19 +7160,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7224,7 +7221,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7239,19 +7236,19 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AL43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7259,14 +7256,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7285,19 +7282,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7346,7 +7343,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7361,19 +7358,19 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AL44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7381,10 +7378,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7407,16 +7404,16 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7466,7 +7463,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7487,13 +7484,13 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7501,10 +7498,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7527,19 +7524,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7588,7 +7585,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7603,19 +7600,19 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AL46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7623,10 +7620,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7649,19 +7646,19 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7686,11 +7683,11 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7708,7 +7705,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7717,7 +7714,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7726,27 +7723,27 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7772,16 +7769,16 @@
         <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7806,14 +7803,14 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="Y48" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="Y48" t="s" s="2">
+      <c r="Z48" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
       </c>
@@ -7830,7 +7827,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7839,7 +7836,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7854,7 +7851,7 @@
         <v>137</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7865,14 +7862,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7894,16 +7891,16 @@
         <v>192</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7928,14 +7925,14 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>400</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
       </c>
@@ -7952,7 +7949,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7970,27 +7967,27 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>404</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8013,19 +8010,19 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8074,7 +8071,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8095,10 +8092,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8109,10 +8106,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8138,13 +8135,13 @@
         <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8170,11 +8167,11 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8192,7 +8189,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8210,27 +8207,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>419</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8256,16 +8253,16 @@
         <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8290,14 +8287,14 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>425</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8314,7 +8311,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8335,10 +8332,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8349,10 +8346,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8375,16 +8372,16 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8434,7 +8431,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8452,27 +8449,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>435</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8495,16 +8492,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8554,7 +8551,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8572,27 +8569,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP54" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>443</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8615,19 +8612,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8676,7 +8673,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8688,19 +8685,19 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AK55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8711,10 +8708,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8829,10 +8826,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8949,14 +8946,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8978,10 +8975,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -9036,7 +9033,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9071,10 +9068,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9097,13 +9094,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9154,7 +9151,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9163,7 +9160,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9175,10 +9172,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9189,10 +9186,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9215,13 +9212,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9272,7 +9269,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9281,7 +9278,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9293,10 +9290,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9307,10 +9304,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9336,16 +9333,16 @@
         <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9373,11 +9370,11 @@
         <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>475</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
       </c>
@@ -9394,7 +9391,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9412,13 +9409,13 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="AM61" t="s" s="2">
-        <v>477</v>
-      </c>
       <c r="AN61" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9429,10 +9426,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9458,16 +9455,16 @@
         <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9492,14 +9489,14 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>484</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9516,7 +9513,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9534,13 +9531,13 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="AM62" t="s" s="2">
-        <v>477</v>
-      </c>
       <c r="AN62" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9551,10 +9548,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9577,17 +9574,17 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="L63" t="s" s="2">
-        <v>487</v>
-      </c>
       <c r="M63" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9636,7 +9633,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9660,7 +9657,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9671,10 +9668,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9700,10 +9697,10 @@
         <v>211</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9754,7 +9751,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9775,10 +9772,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9789,10 +9786,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9815,16 +9812,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9874,7 +9871,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9895,10 +9892,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9909,10 +9906,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9935,16 +9932,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9994,7 +9991,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10015,10 +10012,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10029,10 +10026,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10055,19 +10052,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10116,7 +10113,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10137,10 +10134,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10151,10 +10148,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10269,10 +10266,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10389,14 +10386,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10418,10 +10415,10 @@
         <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>143</v>
@@ -10476,7 +10473,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10511,10 +10508,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10540,16 +10537,16 @@
         <v>192</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="N71" t="s" s="2">
-        <v>517</v>
-      </c>
       <c r="O71" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10574,14 +10571,14 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>519</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10598,7 +10595,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>94</v>
@@ -10616,16 +10613,16 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AN71" t="s" s="2">
+      <c r="AO71" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
@@ -10633,10 +10630,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10659,19 +10656,19 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="N72" t="s" s="2">
-        <v>525</v>
-      </c>
       <c r="O72" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10720,7 +10717,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10738,27 +10735,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AM72" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AN72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>384</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10784,16 +10781,16 @@
         <v>192</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="N73" t="s" s="2">
-        <v>530</v>
-      </c>
       <c r="O73" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10818,14 +10815,14 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="Y73" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="Y73" t="s" s="2">
+      <c r="Z73" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z73" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
       </c>
@@ -10842,7 +10839,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10851,7 +10848,7 @@
         <v>94</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>106</v>
@@ -10866,7 +10863,7 @@
         <v>137</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -10877,14 +10874,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10906,16 +10903,16 @@
         <v>192</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10940,14 +10937,14 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>400</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
       </c>
@@ -10964,7 +10961,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10982,27 +10979,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AN74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>404</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11028,16 +11025,16 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11086,7 +11083,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11107,10 +11104,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2914" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2914" uniqueCount="538">
   <si>
     <t>Property</t>
   </si>
@@ -1171,17 +1171,13 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>CodeableConcept
-string</t>
-  </si>
-  <si>
     <t>内視鏡検査、治療の観察結果（診断、所見など）の情報を格納する。診断、所見の場合、病変単位で記載することが望ましい。【詳細参照】</t>
   </si>
   <si>
     <t>内視鏡検査、治療の観察結果（診断、所見など）の情報を格納する。診断、所見の場合、病変単位で記載することが望ましい。</t>
   </si>
   <si>
-    <t>【JP Core仕様】CodeableConcept：診断、所見情報記載時に使用。text記載は必須とし、必要に応じてcodingも使用する。string：診断、所見以外の情報を記載する際、必要に応じて使用。</t>
+    <t>【JP Core仕様】主に診断、所見情報記載時に使用。text記載は必須とし、必要に応じてcodingも使用する。</t>
   </si>
   <si>
     <t>観測は値を持つように存在しますが、それが誤っている場合、または観測のグループを表す場合はそうではありません。 / An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -7646,19 +7642,19 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7683,11 +7679,11 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7714,7 +7710,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7723,27 +7719,27 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>383</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7769,16 +7765,16 @@
         <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7803,14 +7799,14 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="Y48" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="Y48" t="s" s="2">
+      <c r="Z48" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
       </c>
@@ -7827,7 +7823,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7836,7 +7832,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7851,7 +7847,7 @@
         <v>137</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7862,14 +7858,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7891,16 +7887,16 @@
         <v>192</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7925,14 +7921,14 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>399</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
       </c>
@@ -7949,7 +7945,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7967,27 +7963,27 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>403</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8010,19 +8006,19 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8071,7 +8067,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8092,10 +8088,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8106,10 +8102,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8135,13 +8131,13 @@
         <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8167,11 +8163,11 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8189,7 +8185,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8207,27 +8203,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>418</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8253,16 +8249,16 @@
         <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8287,14 +8283,14 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>424</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8311,7 +8307,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8332,10 +8328,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8346,10 +8342,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8372,16 +8368,16 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8431,7 +8427,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8449,27 +8445,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>434</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8492,16 +8488,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8551,7 +8547,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8569,27 +8565,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP54" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>442</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8612,19 +8608,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8673,7 +8669,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8685,19 +8681,19 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AK55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8708,10 +8704,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8826,10 +8822,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8946,14 +8942,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8975,10 +8971,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -9033,7 +9029,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9068,10 +9064,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9094,13 +9090,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9151,7 +9147,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9160,7 +9156,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9172,10 +9168,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9186,10 +9182,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9212,13 +9208,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9269,7 +9265,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9278,7 +9274,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9290,10 +9286,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9304,10 +9300,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9333,16 +9329,16 @@
         <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9370,11 +9366,11 @@
         <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>474</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
       </c>
@@ -9391,7 +9387,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9409,13 +9405,13 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="AM61" t="s" s="2">
-        <v>476</v>
-      </c>
       <c r="AN61" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9426,10 +9422,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9455,16 +9451,16 @@
         <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9489,14 +9485,14 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>483</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9513,7 +9509,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9531,13 +9527,13 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="AM62" t="s" s="2">
-        <v>476</v>
-      </c>
       <c r="AN62" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9548,10 +9544,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9574,17 +9570,17 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L63" t="s" s="2">
-        <v>486</v>
-      </c>
       <c r="M63" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9633,7 +9629,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9657,7 +9653,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9668,10 +9664,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9697,10 +9693,10 @@
         <v>211</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9751,7 +9747,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9772,10 +9768,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9786,10 +9782,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9812,16 +9808,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9871,7 +9867,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9892,10 +9888,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9906,10 +9902,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9932,16 +9928,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9991,7 +9987,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10012,10 +10008,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10026,10 +10022,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10052,19 +10048,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10113,7 +10109,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10134,10 +10130,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10148,10 +10144,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10266,10 +10262,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10386,14 +10382,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10415,10 +10411,10 @@
         <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>143</v>
@@ -10473,7 +10469,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10508,10 +10504,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10537,13 +10533,13 @@
         <v>192</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="O71" t="s" s="2">
         <v>312</v>
@@ -10571,14 +10567,14 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>518</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10595,7 +10591,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>94</v>
@@ -10613,7 +10609,7 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>316</v>
@@ -10630,10 +10626,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10656,19 +10652,19 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="N72" t="s" s="2">
-        <v>524</v>
-      </c>
       <c r="O72" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10717,7 +10713,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10735,27 +10731,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AM72" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AN72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>383</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10781,16 +10777,16 @@
         <v>192</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="N73" t="s" s="2">
-        <v>529</v>
-      </c>
       <c r="O73" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10815,14 +10811,14 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="Y73" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="Y73" t="s" s="2">
+      <c r="Z73" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="Z73" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
       </c>
@@ -10839,7 +10835,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10848,7 +10844,7 @@
         <v>94</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>106</v>
@@ -10863,7 +10859,7 @@
         <v>137</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -10874,14 +10870,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10903,16 +10899,16 @@
         <v>192</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10937,14 +10933,14 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>399</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
       </c>
@@ -10961,7 +10957,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10979,27 +10975,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AN74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>403</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11025,16 +11021,16 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11083,7 +11079,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11104,10 +11100,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -285,7 +285,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1220,7 +1220,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1407,7 +1407,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1667,7 +1667,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
@@ -2041,7 +2041,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="66.41015625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -2017,15 +2017,15 @@
   <dimension ref="A1:AP75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="47.2890625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.54296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2036,28 +2036,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="66.41015625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.93359375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -3893,7 +3893,7 @@
         <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>83</v>
@@ -5339,7 +5339,7 @@
         <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2914" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="539">
   <si>
     <t>Property</t>
   </si>
@@ -1301,7 +1301,10 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -8165,9 +8168,11 @@
       <c r="X51" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="Y51" s="2"/>
+      <c r="Y51" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8203,27 +8208,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8249,16 +8254,16 @@
         <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8286,10 +8291,10 @@
         <v>376</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8307,7 +8312,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8328,10 +8333,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8342,10 +8347,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8368,16 +8373,16 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8427,7 +8432,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8445,27 +8450,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8488,16 +8493,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8547,7 +8552,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8565,27 +8570,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8608,19 +8613,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8669,7 +8674,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8681,7 +8686,7 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8690,10 +8695,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8704,10 +8709,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8822,10 +8827,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8942,14 +8947,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8971,10 +8976,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -9029,7 +9034,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9064,10 +9069,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9090,13 +9095,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9147,7 +9152,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9156,7 +9161,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9168,10 +9173,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9182,10 +9187,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9208,13 +9213,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9265,7 +9270,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9274,7 +9279,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9286,10 +9291,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9300,10 +9305,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9329,16 +9334,16 @@
         <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9366,10 +9371,10 @@
         <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9387,7 +9392,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9405,10 +9410,10 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>401</v>
@@ -9422,10 +9427,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9451,16 +9456,16 @@
         <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9488,10 +9493,10 @@
         <v>376</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9509,7 +9514,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9527,10 +9532,10 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>401</v>
@@ -9544,10 +9549,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9570,17 +9575,17 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9629,7 +9634,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9653,7 +9658,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9664,10 +9669,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9693,10 +9698,10 @@
         <v>211</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9747,7 +9752,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9768,10 +9773,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9782,10 +9787,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9808,16 +9813,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9867,7 +9872,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9888,10 +9893,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9902,10 +9907,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9928,16 +9933,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9987,7 +9992,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10008,10 +10013,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10022,10 +10027,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10048,19 +10053,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10109,7 +10114,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10130,10 +10135,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10144,10 +10149,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10262,10 +10267,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10382,14 +10387,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10411,10 +10416,10 @@
         <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>143</v>
@@ -10469,7 +10474,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10504,10 +10509,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10533,13 +10538,13 @@
         <v>192</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O71" t="s" s="2">
         <v>312</v>
@@ -10570,10 +10575,10 @@
         <v>376</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10591,7 +10596,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>94</v>
@@ -10609,7 +10614,7 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>316</v>
@@ -10626,10 +10631,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10652,16 +10657,16 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>375</v>
@@ -10713,7 +10718,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10731,7 +10736,7 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>380</v>
@@ -10748,10 +10753,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10777,13 +10782,13 @@
         <v>192</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>386</v>
@@ -10835,7 +10840,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10870,10 +10875,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10899,16 +10904,16 @@
         <v>192</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10957,7 +10962,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10992,10 +10997,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11021,16 +11026,16 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11079,7 +11084,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11100,10 +11105,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -386,7 +386,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -635,7 +635,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -1038,7 +1038,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1223,7 +1223,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1252,7 +1252,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1304,7 +1304,7 @@
     <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1334,7 +1334,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1371,7 +1371,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1446,7 +1446,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1493,7 +1493,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1526,7 +1526,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1634,7 +1634,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR 
--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -3875,7 +3875,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>203</v>
       </c>
@@ -5321,7 +5321,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>290</v>
       </c>
@@ -6889,7 +6889,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>320</v>
       </c>
@@ -7253,7 +7253,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>345</v>
       </c>
@@ -7617,7 +7617,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>371</v>
       </c>
@@ -9785,7 +9785,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>493</v>
       </c>
@@ -11119,12 +11119,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP75">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -638,7 +638,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>94</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -928,6 +928,14 @@
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="LP7796-8"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>Observation.category:second.id</t>
   </si>
   <si>
@@ -944,9 +952,6 @@
   </si>
   <si>
     <t>Observation.category:second.coding.system</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
   </si>
   <si>
     <t>Observation.category:second.coding.version</t>
@@ -5373,7 +5378,7 @@
         <v>83</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>83</v>
@@ -5447,7 +5452,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>210</v>
@@ -5565,7 +5570,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>217</v>
@@ -5685,7 +5690,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>223</v>
@@ -5807,7 +5812,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>233</v>
@@ -5925,7 +5930,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>235</v>
@@ -6045,7 +6050,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>237</v>
@@ -6090,7 +6095,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -1022,7 +1022,7 @@
     <t>このObservationの対象となる患者や患者群、機器、場所に関する情報</t>
   </si>
   <si>
-    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明なデバイスによって観察が行われるケースである。この場合、観察は何らかのコンテキスト/チャネルマッチング技術を介して患者にマッチングされる必要があり、患者にマッチングされれば、その時点で本要素を更新する必要がある。</t>
+    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明な機器によって観察が行われるケースである。この場合、観察は何らかのコンテキスト・チャネル照合技術を介して患者に照合される必要があり、患者に照合されれば、その時点で本要素を更新する必要がある。</t>
   </si>
   <si>
     <t>あなたが彼らが誰または何をしているのかわからない場合、観察には価値がありません。 / Observations have no value if you don't know who or what they're about.</t>
@@ -1383,7 +1383,7 @@
     <t>このObservationでデータを得るために使われた測定機器に関する情報</t>
   </si>
   <si>
-    <t>これは、結果の送信に関与するデバイス（ゲートウェイなど）を表すことを意図したものではない。そのようなデバイスは、必要に応じてProvenanceリソースを使用して文書化する。</t>
+    <t>これは、結果の送信に関与する機器（ゲートウェイなど）を表すことを意図したものではない。そのような機器は、必要に応じてProvenanceリソースを使用して文書化する。</t>
   </si>
   <si>
     <t>&lt; 49062001 |Device|</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="538">
   <si>
     <t>Property</t>
   </si>
@@ -666,6 +666,14 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
+    &lt;code value="procedure"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
@@ -820,9 +828,6 @@
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>procedure</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -958,9 +963,6 @@
   </si>
   <si>
     <t>Observation.category:second.coding.code</t>
-  </si>
-  <si>
-    <t>LP7796-8</t>
   </si>
   <si>
     <t>Observation.category:second.coding.display</t>
@@ -3932,7 +3934,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -3951,7 +3953,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4004,10 +4006,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4030,13 +4032,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4087,7 +4089,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4111,7 +4113,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4122,10 +4124,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4154,7 +4156,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4195,10 +4197,10 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
@@ -4207,7 +4209,7 @@
         <v>200</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4231,7 +4233,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4242,10 +4244,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4268,19 +4270,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4329,7 +4331,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4350,10 +4352,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4364,10 +4366,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4390,13 +4392,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4447,7 +4449,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4471,7 +4473,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4482,10 +4484,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4514,7 +4516,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4555,10 +4557,10 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
@@ -4567,7 +4569,7 @@
         <v>200</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4591,7 +4593,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4602,10 +4604,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4631,23 +4633,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4689,7 +4691,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4710,10 +4712,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4724,10 +4726,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4750,16 +4752,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4809,7 +4811,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4830,10 +4832,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4844,10 +4846,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4873,21 +4875,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>259</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4990,7 +4992,7 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>265</v>
@@ -5232,7 +5234,7 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>283</v>
@@ -5455,7 +5457,7 @@
         <v>295</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5478,13 +5480,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5535,7 +5537,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5559,7 +5561,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5573,7 +5575,7 @@
         <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5602,7 +5604,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5643,10 +5645,10 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
@@ -5655,7 +5657,7 @@
         <v>200</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5679,7 +5681,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5693,7 +5695,7 @@
         <v>297</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5716,19 +5718,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5777,7 +5779,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5798,10 +5800,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5815,7 +5817,7 @@
         <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5838,13 +5840,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5895,7 +5897,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5919,7 +5921,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5933,7 +5935,7 @@
         <v>299</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5962,7 +5964,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -6003,10 +6005,10 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
@@ -6015,7 +6017,7 @@
         <v>200</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6039,7 +6041,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6053,7 +6055,7 @@
         <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6079,16 +6081,16 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6137,7 +6139,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6158,10 +6160,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6175,7 +6177,7 @@
         <v>301</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6198,16 +6200,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6257,7 +6259,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6278,10 +6280,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6295,7 +6297,7 @@
         <v>302</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6321,21 +6323,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>303</v>
+        <v>83</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6412,7 +6414,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>264</v>
@@ -6438,7 +6440,7 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>265</v>
@@ -6532,7 +6534,7 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>272</v>
@@ -6654,7 +6656,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>282</v>
@@ -6680,7 +6682,7 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>283</v>
@@ -6776,14 +6778,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6805,16 +6807,16 @@
         <v>192</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6843,7 +6845,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6861,7 +6863,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>94</v>
@@ -6876,30 +6878,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>319</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6922,19 +6924,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6983,7 +6985,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6998,19 +7000,19 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AL41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>83</v>
@@ -7018,10 +7020,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7044,16 +7046,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7103,7 +7105,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7124,13 +7126,13 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7138,14 +7140,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7164,19 +7166,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7225,7 +7227,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7240,19 +7242,19 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AL43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7260,14 +7262,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7286,19 +7288,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7347,7 +7349,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7362,19 +7364,19 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AL44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7382,10 +7384,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7408,16 +7410,16 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7467,7 +7469,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7488,13 +7490,13 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7502,10 +7504,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7528,19 +7530,19 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7589,7 +7591,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7604,19 +7606,19 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AL46" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AN46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7624,10 +7626,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7653,16 +7655,16 @@
         <v>192</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7687,11 +7689,11 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7709,7 +7711,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7718,7 +7720,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7727,27 +7729,27 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>382</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7773,16 +7775,16 @@
         <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7807,14 +7809,14 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="Y48" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="Y48" t="s" s="2">
+      <c r="Z48" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>389</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
       </c>
@@ -7831,7 +7833,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7840,7 +7842,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7855,7 +7857,7 @@
         <v>137</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7866,14 +7868,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7895,16 +7897,16 @@
         <v>192</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="M49" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7929,14 +7931,14 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
       </c>
@@ -7953,7 +7955,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7971,27 +7973,27 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>402</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8014,19 +8016,19 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>406</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8075,7 +8077,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8096,10 +8098,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8110,10 +8112,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8139,13 +8141,13 @@
         <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8171,14 +8173,14 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="Z51" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="Z51" t="s" s="2">
-        <v>414</v>
-      </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
       </c>
@@ -8195,7 +8197,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8213,27 +8215,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>418</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8259,16 +8261,16 @@
         <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M52" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8293,14 +8295,14 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>424</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8317,7 +8319,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8338,10 +8340,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8352,10 +8354,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8378,16 +8380,16 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8437,7 +8439,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8455,27 +8457,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AN53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>434</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8498,16 +8500,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8557,7 +8559,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8575,27 +8577,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP54" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>442</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8618,19 +8620,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8679,7 +8681,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8691,19 +8693,19 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AK55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8714,10 +8716,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8740,13 +8742,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8797,7 +8799,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8821,7 +8823,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8832,10 +8834,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8864,7 +8866,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -8917,7 +8919,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8941,7 +8943,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -8952,14 +8954,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8981,10 +8983,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -9039,7 +9041,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9074,10 +9076,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9100,13 +9102,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9157,7 +9159,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9166,7 +9168,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9178,10 +9180,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9192,10 +9194,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9218,13 +9220,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9275,7 +9277,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9284,7 +9286,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9296,10 +9298,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9310,10 +9312,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9339,16 +9341,16 @@
         <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9376,11 +9378,11 @@
         <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="Z61" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>474</v>
-      </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
       </c>
@@ -9397,7 +9399,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9415,13 +9417,13 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="AM61" t="s" s="2">
-        <v>476</v>
-      </c>
       <c r="AN61" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9432,10 +9434,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9461,16 +9463,16 @@
         <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9495,14 +9497,14 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>483</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9519,7 +9521,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9537,13 +9539,13 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="AM62" t="s" s="2">
-        <v>476</v>
-      </c>
       <c r="AN62" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9554,10 +9556,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9580,17 +9582,17 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="L63" t="s" s="2">
-        <v>486</v>
-      </c>
       <c r="M63" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9639,7 +9641,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9663,7 +9665,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9674,10 +9676,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9700,13 +9702,13 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9757,7 +9759,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9778,10 +9780,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9792,10 +9794,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9818,16 +9820,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9877,7 +9879,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9898,10 +9900,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9912,10 +9914,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9938,16 +9940,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9997,7 +9999,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10018,10 +10020,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10032,10 +10034,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10058,19 +10060,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10119,7 +10121,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10140,10 +10142,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10154,10 +10156,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10180,13 +10182,13 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10237,7 +10239,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10261,7 +10263,7 @@
         <v>83</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10272,10 +10274,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10304,7 +10306,7 @@
         <v>141</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>143</v>
@@ -10357,7 +10359,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10381,7 +10383,7 @@
         <v>83</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10392,14 +10394,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10421,10 +10423,10 @@
         <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>143</v>
@@ -10479,7 +10481,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10514,10 +10516,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10543,16 +10545,16 @@
         <v>192</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="N71" t="s" s="2">
-        <v>516</v>
-      </c>
       <c r="O71" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10577,14 +10579,14 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>518</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10601,7 +10603,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>94</v>
@@ -10619,16 +10621,16 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AN71" t="s" s="2">
+      <c r="AO71" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>83</v>
@@ -10636,10 +10638,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10662,19 +10664,19 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="N72" t="s" s="2">
-        <v>524</v>
-      </c>
       <c r="O72" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10723,7 +10725,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10741,27 +10743,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AM72" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AN72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>382</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10787,16 +10789,16 @@
         <v>192</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="N73" t="s" s="2">
-        <v>529</v>
-      </c>
       <c r="O73" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10821,14 +10823,14 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="Y73" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="Y73" t="s" s="2">
+      <c r="Z73" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="Z73" t="s" s="2">
-        <v>389</v>
-      </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
       </c>
@@ -10845,7 +10847,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10854,7 +10856,7 @@
         <v>94</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>106</v>
@@ -10869,7 +10871,7 @@
         <v>137</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -10880,14 +10882,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10909,16 +10911,16 @@
         <v>192</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10943,14 +10945,14 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>398</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
       </c>
@@ -10967,7 +10969,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10985,27 +10987,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AN74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>402</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11031,16 +11033,16 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N75" t="s" s="2">
+      <c r="O75" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11089,7 +11091,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11110,10 +11112,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -552,7 +552,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -1024,7 +1024,7 @@
     <t>このObservationの対象となる患者や患者群、機器、場所に関する情報</t>
   </si>
   <si>
-    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明な機器によって観察が行われるケースである。この場合、観察は何らかのコンテキスト・チャネル照合技術を介して患者に照合される必要があり、患者に照合されれば、その時点で本要素を更新する必要がある。</t>
+    <t>原則subjectを記述すべきだが、対象患者が不明なデバイス観察のケースを考慮し、cardinalityは0..1とする。</t>
   </si>
   <si>
     <t>あなたが彼らが誰または何をしているのかわからない場合、観察には価値がありません。 / Observations have no value if you don't know who or what they're about.</t>
@@ -1608,7 +1608,7 @@
     <t>複数のObservation をグループに一緒にまとめる方法については、以下の[Notes]（observation.html＃notes）を参照すること。</t>
   </si>
   <si>
-    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではないん）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
+    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではない）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
